--- a/data/ca_template.xlsx
+++ b/data/ca_template.xlsx
@@ -6481,7 +6481,7 @@
       </c>
       <c r="B1" s="339" t="inlineStr">
         <is>
-          <t>5.4.7</t>
+          <t>5.4.9</t>
         </is>
       </c>
     </row>
